--- a/diseases/d199/2005-2009.xlsx
+++ b/diseases/d199/2005-2009.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19161,7 +19161,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19950,7 +19950,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20739,7 +20739,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22317,7 +22317,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23106,7 +23106,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23895,7 +23895,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25473,7 +25473,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27840,7 +27840,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29418,7 +29418,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30207,7 +30207,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33363,7 +33363,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34941,7 +34941,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35730,7 +35730,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38097,7 +38097,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38886,7 +38886,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -39823,7 +39823,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -40760,7 +40760,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41697,7 +41697,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -42634,7 +42634,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43571,7 +43571,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45445,7 +45445,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -46382,7 +46382,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47319,7 +47319,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -48256,7 +48256,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN250" t="b">

--- a/diseases/d199/2005-2009.xlsx
+++ b/diseases/d199/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15995,7 +15995,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19940,7 +19940,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20729,7 +20729,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29408,7 +29408,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31775,7 +31775,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34142,7 +34142,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36509,7 +36509,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38876,7 +38876,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -39813,7 +39813,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
@@ -40750,7 +40750,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -41687,7 +41687,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -42624,7 +42624,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43561,7 +43561,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45435,7 +45435,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
@@ -46372,7 +46372,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47309,7 +47309,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -48246,7 +48246,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -49183,7 +49183,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
